--- a/pacjenci/MARTA FISZBAIN.xlsx
+++ b/pacjenci/MARTA FISZBAIN.xlsx
@@ -485,12 +485,12 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -529,12 +529,12 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -542,17 +542,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -586,17 +586,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">

--- a/pacjenci/MARTA FISZBAIN.xlsx
+++ b/pacjenci/MARTA FISZBAIN.xlsx
@@ -413,235 +413,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>13.09.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy (grudkowy) G1- rozpoznanie na podstawie wycinka guza przestrzeni zaotrzewnowej korzenia krezki jelita cienkiego. Ocena zaawansowania klinicznego.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 102 mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Pobudzone metabolicznie węzły chłonne: -pachowe prawe wielkości do 13 mm SUV max do 2,7 -pachowe lewe wielkości do 10 mm SUV max do 2,7 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.  Brzuch i miednica: Aktywne metabolicznie miękkotkankowe nacieki w śródbrzuszu pośrodkowo i po stronie lewej w obrębie krezki wielkości do 96x40 mm wg PET [Im fuz. 179] na długości do 157 mm wg PET SUV max do 9,0. Wzmożony metabolizm FDG w w topografii jelit w śródbrzuszu po stronie lewej SUV max do 7,2.  Pobudzone metabolicznie węzły chłonne: - pachwinowe prawe wielkości do 10 mm SUV max do 3,2 - pachwinowe lewe wielkości do 9 mm SUV max do 2,6. Wzmożony metabolizm FDG w  śledzionie SUV max do 4,2. Rozlanie wzmożony metabolizm FDG w żołądku SUV max do 4,7- odczynowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Aktywny metabolicznie obszar w kości biodrowej lewej wielkości 15x29 mm wg PET SUV max 7,2. Aktywny metabolicznej obszar w szparze stawu biodrowego lewego SUV max 4,7- niejednoznaczny. Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowe kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym oraz na poziomie L5/S1.  Wartości referencyjne: MBPS SUVmax 1,9 Prawy płat wątroby SUVmax do 3,2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego z zajęciem krezki, kości biodrowej lewej oraz węzłów chłonnych po obu stronach przepony.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>9</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>13.12.2021</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy (grudkowy) G1- rozpoznanie na podstawie wycinka guza przestrzeni zaotrzewnowej korzenia krezki jelita cienkiego. Ocena remisji choroby po 3 cyklach chemioterapii.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 63 min od podania 18F-FDG. Glikemia: 108 mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony miernie nasilony zanik korowo-podkorowy mózgu. Wydatne lewowypukłe skrzywienie części środkowej przegrody nosowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowo zwiększony metabolizm FDG w topografii pętli jelitowych -czynnościowo? Zwiększony metabolizm FDG w części wpustowej żołądka- odczynowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wzmożenie gęstości tkanki tłuszczowej okołokrezkowej oraz węzły chłonne krezkowe wielkości do 11mm.  Układ kostny: Aktywny metabolicznie obszar w kości biodrowej lewej wielkości 15x29 mm wg PET, SUV max 7,2. Aktywny metabolicznej obszar w topografii szpary stawowej stawu biodrowego lewego, SUV max 4,1- niejednoznaczny. Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Lewowypukła skolioza na pograniczu szyjno-piersiowym oraz niewielka prawowypukła w odcinku lędźwiowym kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym i piersiowym kregosłupa. Ciasna dyskopatia na poziomie L5/S1. Zmiany zwyrodnieniowo-wytwórcze Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 3,6.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnego metabolicznie procesu chłoniakowego. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>7.2</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>17.03.2022</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>chłoniak nieziarniczy (grudkowy) G1- ocena remisji choroby po 6 cyklach O-CVP.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 111 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony miernie nasilony zanik korowo-podkorowy mózgu. Wydatne lewowypukłe skrzywienie części środkowej przegrody nosowej. Tarczyca miernie powiększona, o nieco niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli endokrynologicznej i w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowo zwiększony metabolizm FDG w topografii pętli jelita grubego i żołądka - niecharakterystyczny do ew. oceny endoskopowej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wzmożenie gęstości w przeglądowym badaniu TK tkanki tłuszczowej okołokrezkowo oraz powiększone węzły chłonne krezkowe, zwłaszcza po stronie lewej, wielkości do ok. 14x11 mm.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Lewowypukła skolioza na pograniczu szyjno-piersiowym oraz niewielka prawowypukła w odcinku lędźwiowym kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym i piersiowym kregosłupa. Ciasna dyskopatia na poziomie L5/S1. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Os sacrum arcuatum.  Inne: Rozlanie wzmożony metabolizm FDG w obrębie mięśni, zwłaszcza mięśni stożków rotatorów, mięśni grzbietu, mięśni ud oraz pośladków obustronnie - w pierwszej kolejności przeciążeniowo, SUVmax do 7,0 (m. podłopatkowy lewy).  Wartości referencyjne: MBPS SUVmax do 1,2; Prawy płat wątroby SUVmax do 2,8.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Aktualnie badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnego metabolicznie procesu chłoniakowego.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>7</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>22.11.2022</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy (grudkowy) G1- ocena remisji choroby.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 93 mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony miernie nasilony zanik korowo-podkorowy mózgu. Wydatne lewowypukłe skrzywienie części środkowej przegrody nosowej. Tarczyca miernie powiększona, o nieco niejednorodnym cieniowaniu w przeglądowym badaniu TK.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowo zwiększony metabolizm FDG w topografii pętli jelita grubego i żołądka - niecharakterystyczny. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wzmożenie gęstości w przeglądowym badaniu TK tkanki tłuszczowej okołokrezkowo oraz dość liczne, drobne węzły chłonne krezkowe, zwłaszcza po stronie lewej.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa z odcinkowym pobudzeniem metabolicznym.  Lewowypukła skolioza na pograniczu szyjno-piersiowym oraz niewielka prawowypukła w odcinku lędźwiowym kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym i piersiowym kregosłupa. Ciasna dyskopatia na poziomie L5/S1. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Drobna wyspa kostna w głowie prawej kości udowej.  Inne: Niejednoznaczny obszar pobudzenie metabolicznego w przyleganiu do głowy kości ramiennej lewej, w drobnym odszczepem kostnym? SUV max 4,2- do kontroli/ weryfikacji.  Wartości referencyjne: MBPS SUVmax do 2,6; Prawy płat wątroby SUVmax do 4,1.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktualnie badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnych metabolicznie węzłów chłonnych. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>4.2</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/MARTA FISZBAIN.xlsx
+++ b/pacjenci/MARTA FISZBAIN.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 102 mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Pobudzone metabolicznie węzły chłonne: -pachowe prawe wielkości do 13 mm SUV max do 2,7 -pachowe lewe wielkości do 10 mm SUV max do 2,7 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.  Brzuch i miednica: Aktywne metabolicznie miękkotkankowe nacieki w śródbrzuszu pośrodkowo i po stronie lewej w obrębie krezki wielkości do 96x40 mm wg PET [Im fuz. 179] na długości do 157 mm wg PET SUV max do 9,0. Wzmożony metabolizm FDG w w topografii jelit w śródbrzuszu po stronie lewej SUV max do 7,2.  Pobudzone metabolicznie węzły chłonne: - pachwinowe prawe wielkości do 10 mm SUV max do 3,2 - pachwinowe lewe wielkości do 9 mm SUV max do 2,6. Wzmożony metabolizm FDG w  śledzionie SUV max do 4,2. Rozlanie wzmożony metabolizm FDG w żołądku SUV max do 4,7- odczynowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Aktywny metabolicznie obszar w kości biodrowej lewej wielkości 15x29 mm wg PET SUV max 7,2. Aktywny metabolicznej obszar w szparze stawu biodrowego lewego SUV max 4,7- niejednoznaczny. Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowe kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym oraz na poziomie L5/S1.  Wartości referencyjne: MBPS SUVmax 1,9 Prawy płat wątroby SUVmax do 3,2</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Pobudzone metabolicznie węzły chłonne: -pachowe prawe wielkości do 13 mm SUV max do 2,7 -pachowe lewe wielkości do 10 mm SUV max do 2,7 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie miękkotkankowe nacieki w śródbrzuszu pośrodkowo i po stronie lewej w obrębie krezki wielkości do 96x40 mm wg PET [Im fuz. 179] na długości do 157 mm wg PET SUV max do 9,0. Wzmożony metabolizm FDG w w topografii jelit w śródbrzuszu po stronie lewej SUV max do 7,2.  Pobudzone metabolicznie węzły chłonne: - pachwinowe prawe wielkości do 10 mm SUV max do 3,2 - pachwinowe lewe wielkości do 9 mm SUV max do 2,6. Wzmożony metabolizm FDG w  śledzionie SUV max do 4,2. Rozlanie wzmożony metabolizm FDG w żołądku SUV max do 4,7- odczynowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w kości biodrowej lewej wielkości 15x29 mm wg PET SUV max 7,2. Aktywny metabolicznej obszar w szparze stawu biodrowego lewego SUV max 4,7- niejednoznaczny. Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowe kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym oraz na poziomie L5/S1.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego z zajęciem krezki, kości biodrowej lewej oraz węzłów chłonnych po obu stronach przepony.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>9</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 63 min od podania 18F-FDG. Glikemia: 108 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony miernie nasilony zanik korowo-podkorowy mózgu. Wydatne lewowypukłe skrzywienie części środkowej przegrody nosowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowo zwiększony metabolizm FDG w topografii pętli jelitowych -czynnościowo? Zwiększony metabolizm FDG w części wpustowej żołądka- odczynowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wzmożenie gęstości tkanki tłuszczowej okołokrezkowej oraz węzły chłonne krezkowe wielkości do 11mm.  Układ kostny: Aktywny metabolicznie obszar w kości biodrowej lewej wielkości 15x29 mm wg PET, SUV max 7,2. Aktywny metabolicznej obszar w topografii szpary stawowej stawu biodrowego lewego, SUV max 4,1- niejednoznaczny. Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Lewowypukła skolioza na pograniczu szyjno-piersiowym oraz niewielka prawowypukła w odcinku lędźwiowym kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym i piersiowym kregosłupa. Ciasna dyskopatia na poziomie L5/S1. Zmiany zwyrodnieniowo-wytwórcze Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 3,6.</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony miernie nasilony zanik korowo-podkorowy mózgu. Wydatne lewowypukłe skrzywienie części środkowej przegrody nosowej.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Odcinkowo zwiększony metabolizm FDG w topografii pętli jelitowych -czynnościowo? Zwiększony metabolizm FDG w części wpustowej żołądka- odczynowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wzmożenie gęstości tkanki tłuszczowej okołokrezkowej oraz węzły chłonne krezkowe wielkości do 11mm.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w kości biodrowej lewej wielkości 15x29 mm wg PET, SUV max 7,2. Aktywny metabolicznej obszar w topografii szpary stawowej stawu biodrowego lewego, SUV max 4,1- niejednoznaczny. Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Lewowypukła skolioza na pograniczu szyjno-piersiowym oraz niewielka prawowypukła w odcinku lędźwiowym kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym i piersiowym kregosłupa. Ciasna dyskopatia na poziomie L5/S1. Zmiany zwyrodnieniowo-wytwórcze Os sacrum arcuatum.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnego metabolicznie procesu chłoniakowego. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>7.2</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 111 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony miernie nasilony zanik korowo-podkorowy mózgu. Wydatne lewowypukłe skrzywienie części środkowej przegrody nosowej. Tarczyca miernie powiększona, o nieco niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli endokrynologicznej i w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowo zwiększony metabolizm FDG w topografii pętli jelita grubego i żołądka - niecharakterystyczny do ew. oceny endoskopowej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wzmożenie gęstości w przeglądowym badaniu TK tkanki tłuszczowej okołokrezkowo oraz powiększone węzły chłonne krezkowe, zwłaszcza po stronie lewej, wielkości do ok. 14x11 mm.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Lewowypukła skolioza na pograniczu szyjno-piersiowym oraz niewielka prawowypukła w odcinku lędźwiowym kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym i piersiowym kregosłupa. Ciasna dyskopatia na poziomie L5/S1. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Os sacrum arcuatum.  Inne: Rozlanie wzmożony metabolizm FDG w obrębie mięśni, zwłaszcza mięśni stożków rotatorów, mięśni grzbietu, mięśni ud oraz pośladków obustronnie - w pierwszej kolejności przeciążeniowo, SUVmax do 7,0 (m. podłopatkowy lewy).  Wartości referencyjne: MBPS SUVmax do 1,2; Prawy płat wątroby SUVmax do 2,8.</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony miernie nasilony zanik korowo-podkorowy mózgu. Wydatne lewowypukłe skrzywienie części środkowej przegrody nosowej. Tarczyca miernie powiększona, o nieco niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli endokrynologicznej i w USG.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Odcinkowo zwiększony metabolizm FDG w topografii pętli jelita grubego i żołądka - niecharakterystyczny do ew. oceny endoskopowej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wzmożenie gęstości w przeglądowym badaniu TK tkanki tłuszczowej okołokrezkowo oraz powiększone węzły chłonne krezkowe, zwłaszcza po stronie lewej, wielkości do ok. 14x11 mm.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Lewowypukła skolioza na pograniczu szyjno-piersiowym oraz niewielka prawowypukła w odcinku lędźwiowym kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym i piersiowym kregosłupa. Ciasna dyskopatia na poziomie L5/S1. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Os sacrum arcuatum.  Inne: Rozlanie wzmożony metabolizm FDG w obrębie mięśni, zwłaszcza mięśni stożków rotatorów, mięśni grzbietu, mięśni ud oraz pośladków obustronnie - w pierwszej kolejności przeciążeniowo, SUVmax do 7,0 (m. podłopatkowy lewy).</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Aktualnie badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnego metabolicznie procesu chłoniakowego.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>7</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 93 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony miernie nasilony zanik korowo-podkorowy mózgu. Wydatne lewowypukłe skrzywienie części środkowej przegrody nosowej. Tarczyca miernie powiększona, o nieco niejednorodnym cieniowaniu w przeglądowym badaniu TK.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowo zwiększony metabolizm FDG w topografii pętli jelita grubego i żołądka - niecharakterystyczny. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wzmożenie gęstości w przeglądowym badaniu TK tkanki tłuszczowej okołokrezkowo oraz dość liczne, drobne węzły chłonne krezkowe, zwłaszcza po stronie lewej.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa z odcinkowym pobudzeniem metabolicznym.  Lewowypukła skolioza na pograniczu szyjno-piersiowym oraz niewielka prawowypukła w odcinku lędźwiowym kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym i piersiowym kregosłupa. Ciasna dyskopatia na poziomie L5/S1. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Drobna wyspa kostna w głowie prawej kości udowej.  Inne: Niejednoznaczny obszar pobudzenie metabolicznego w przyleganiu do głowy kości ramiennej lewej, w drobnym odszczepem kostnym? SUV max 4,2- do kontroli/ weryfikacji.  Wartości referencyjne: MBPS SUVmax do 2,6; Prawy płat wątroby SUVmax do 4,1.</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony miernie nasilony zanik korowo-podkorowy mózgu. Wydatne lewowypukłe skrzywienie części środkowej przegrody nosowej. Tarczyca miernie powiększona, o nieco niejednorodnym cieniowaniu w przeglądowym badaniu TK.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc oraz obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Odcinkowo zwiększony metabolizm FDG w topografii pętli jelita grubego i żołądka - niecharakterystyczny. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wzmożenie gęstości w przeglądowym badaniu TK tkanki tłuszczowej okołokrezkowo oraz dość liczne, drobne węzły chłonne krezkowe, zwłaszcza po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa z odcinkowym pobudzeniem metabolicznym.  Lewowypukła skolioza na pograniczu szyjno-piersiowym oraz niewielka prawowypukła w odcinku lędźwiowym kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym i piersiowym kregosłupa. Ciasna dyskopatia na poziomie L5/S1. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Drobna wyspa kostna w głowie prawej kości udowej.  Inne: Niejednoznaczny obszar pobudzenie metabolicznego w przyleganiu do głowy kości ramiennej lewej, w drobnym odszczepem kostnym? SUV max 4,2- do kontroli/ weryfikacji.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Aktualnie badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnych metabolicznie węzłów chłonnych. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>4.2</v>
       </c>
     </row>
